--- a/EKG_Kalite_Yönetim_Sistemi/02_Proje ve Ürün-Proses Yeterliliği/01_CMG1 - APQP, Fizibilite ve Kaynaklar/EKG-PRJ-MTR-01_proje_kaynak_ve_is_yuku_matrisi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/02_Proje ve Ürün-Proses Yeterliliği/01_CMG1 - APQP, Fizibilite ve Kaynaklar/EKG-PRJ-MTR-01_proje_kaynak_ve_is_yuku_matrisi.xlsx
@@ -1055,7 +1055,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-MTR-01&amp;C&amp;"Arial,Regular"&amp;11Proje Kaynak ve İş Yükü Matrisi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 02.06.2026 | Revizyon: 02.09.2026
+Revizyon nedeni: Mevcut kaynak hesabı korundu; vardiya/rol bazında aynı kişinin çift sayılması önlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bcbeff35fc94162"/>
   <x:tableParts count="1">
@@ -1538,7 +1539,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-MTR-01&amp;C&amp;"Arial,Regular"&amp;11Proje Kaynak ve İş Yükü Matrisi</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 02.06.2026 | Revizyon: 02.09.2026
+Revizyon nedeni: Mevcut kaynak hesabı korundu; vardiya/rol bazında aynı kişinin çift sayılması önlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0657725d958b40dd"/>
   <x:tableParts count="1">
